--- a/results/aggregates/ai_fiscal_publishable_2030_latest.xlsx
+++ b/results/aggregates/ai_fiscal_publishable_2030_latest.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-05-26 12:18:04 EDT</t>
+    <t xml:space="preserve">2026-05-26 13:27:05 EDT</t>
   </si>
   <si>
     <t xml:space="preserve">Bundle type</t>
@@ -58,13 +58,13 @@
     <t xml:space="preserve">Tax-Simulator vintage</t>
   </si>
   <si>
-    <t xml:space="preserve">202605261209</t>
+    <t xml:space="preserve">202605261319</t>
   </si>
   <si>
     <t xml:space="preserve">Tax-Simulator output root</t>
   </si>
   <si>
-    <t xml:space="preserve">/nfs/roberts/project/pi_nrs36/ji252/scratch/tax_sim/model_data/Tax-Simulator/v1/202605261209</t>
+    <t xml:space="preserve">/nfs/roberts/project/pi_nrs36/ji252/scratch/tax_sim/model_data/Tax-Simulator/v1/202605261319</t>
   </si>
   <si>
     <t xml:space="preserve">Runscript</t>
@@ -94,7 +94,7 @@
     <t xml:space="preserve">ai_fiscal git rev</t>
   </si>
   <si>
-    <t xml:space="preserve">41bbc6df3e2b</t>
+    <t xml:space="preserve">471d9124dd00</t>
   </si>
   <si>
     <t xml:space="preserve">Orchestrator argv</t>

--- a/results/aggregates/ai_fiscal_publishable_2030_latest.xlsx
+++ b/results/aggregates/ai_fiscal_publishable_2030_latest.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="499" uniqueCount="499">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="507" uniqueCount="507">
   <si>
     <t xml:space="preserve">field</t>
   </si>
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-22 15:41:48 EDT</t>
+    <t xml:space="preserve">2026-06-30 00:20:46 EDT</t>
   </si>
   <si>
     <t xml:space="preserve">Bundle type</t>
@@ -58,13 +58,13 @@
     <t xml:space="preserve">Tax-Simulator vintage</t>
   </si>
   <si>
-    <t xml:space="preserve">202606221535</t>
+    <t xml:space="preserve">202606300013</t>
   </si>
   <si>
     <t xml:space="preserve">Tax-Simulator output root</t>
   </si>
   <si>
-    <t xml:space="preserve">/nfs/roberts/scratch/pi_nrs36/jar335/model_data/Tax-Simulator/v1/202606221535</t>
+    <t xml:space="preserve">/nfs/roberts/scratch/pi_nrs36/ji252/model_data/Tax-Simulator/v1/202606300013</t>
   </si>
   <si>
     <t xml:space="preserve">Runscript</t>
@@ -94,7 +94,7 @@
     <t xml:space="preserve">AI-Fiscal git rev</t>
   </si>
   <si>
-    <t xml:space="preserve">f832339471cb</t>
+    <t xml:space="preserve">4a1111ae1e12</t>
   </si>
   <si>
     <t xml:space="preserve">Orchestrator argv</t>
@@ -133,10 +133,10 @@
     <t xml:space="preserve">5-yr cumulative shock target</t>
   </si>
   <si>
-    <t xml:space="preserve">K1 = s1*(1+gy); L1 = (1-s1)*(1+gy); gk = (K1-K0)/K0; alpha = (1/gk) * (L1-L0)/L0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s1=0.450, gy=0.0060 -&gt; gk ≈ +1.7%,  alpha ≈ -0.18 -&gt; labor -0.3%  (Slow)</t>
+    <t xml:space="preserve">g_k = (theta1_k*(1+g_y) - theta0_k)/theta0_k; g_l = (theta1_l*(1+g_y) - theta0_l)/theta0_l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theta1_k=0.450, g_y=0.0060 -&gt; g_k ≈ +1.7%,  g_l ≈ -0.3%  (Slow)</t>
   </si>
   <si>
     <t xml:space="preserve">M</t>
@@ -148,7 +148,7 @@
     <t xml:space="preserve">(same as S)</t>
   </si>
   <si>
-    <t xml:space="preserve">s1=0.462, gy=0.0358 -&gt; gk ≈ +7.5%,  alpha ≈ +0.05 -&gt; labor +0.4%  (Moderate)</t>
+    <t xml:space="preserve">theta1_k=0.462, g_y=0.0358 -&gt; g_k ≈ +7.5%,  g_l ≈ +0.4%  (Moderate)</t>
   </si>
   <si>
     <t xml:space="preserve">R</t>
@@ -157,7 +157,7 @@
     <t xml:space="preserve">Rapid</t>
   </si>
   <si>
-    <t xml:space="preserve">s1=0.487, gy=0.0716 -&gt; gk ≈ +17.3%, alpha ≈ -0.05 -&gt; labor -0.9% (Rapid)</t>
+    <t xml:space="preserve">theta1_k=0.487, g_y=0.0716 -&gt; g_k ≈ +17.3%, g_l ≈ -0.9% (Rapid)</t>
   </si>
   <si>
     <t xml:space="preserve">share_mode</t>
@@ -166,10 +166,10 @@
     <t xml:space="preserve">Reallocate</t>
   </si>
   <si>
-    <t xml:space="preserve">Karger labor-share decline: s1 from yaml</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s1 from yaml shock.variants.&lt;variant&gt;.s1; gk and alpha derived as above.</t>
+    <t xml:space="preserve">Karger labor-share decline: theta1_k from yaml</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theta1_k from yaml shock.variants.&lt;variant&gt;.theta1_k; g_k and g_l derived as above.</t>
   </si>
   <si>
     <t xml:space="preserve">Canonical AI-growth-plus-reallocation shock.</t>
@@ -181,13 +181,13 @@
     <t xml:space="preserve">Fixed share</t>
   </si>
   <si>
-    <t xml:space="preserve">Hold labor-capital share at baseline: s1 := 1 - L0</t>
-  </si>
-  <si>
-    <t xml:space="preserve">s1 = 1 - L0 = K0  =&gt;  gk = gy, alpha = 1; labor and capital both grow at gy.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Paired twin of R: same gy, labor and capital both scale by (1+gy).</t>
+    <t xml:space="preserve">Hold labor-capital share at baseline: theta1_k := theta0_k</t>
+  </si>
+  <si>
+    <t xml:space="preserve">theta1_k = theta0_k  =&gt;  g_k = g_l = g_y; labor and capital both grow at g_y.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Paired twin of R: same g_y, labor and capital both scale by (1+g_y).</t>
   </si>
   <si>
     <t xml:space="preserve">labor</t>
@@ -199,13 +199,13 @@
     <t xml:space="preserve">Compressive</t>
   </si>
   <si>
-    <t xml:space="preserve">Log-affine, sigma_S2 = 1 - k_inequality * gy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ln(YiL1) = mu1 + sigma_S2 * (ln(YiL0) - mu0); sigma_S2 = 1 - k_inequality * gy; mu1 via uniroot to hit L1$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">k_inequality = 1 by default (config: labor_inequality.k). See labor_inequality sheet for per-variant sigma_S2.</t>
+    <t xml:space="preserve">Log-affine, lambda_S2 = 1 - k_inequality * g_y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ln(y_l1) = mu1 + lambda_S2 * (ln(y_l) - mu0); lambda_S2 = 1 - k_inequality * g_y; mu1 via uniroot to hit Y1^L$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k_inequality = 1 by default (config: labor_inequality.k). See labor_inequality sheet for per-variant lambda_S2.</t>
   </si>
   <si>
     <t xml:space="preserve">S0</t>
@@ -217,7 +217,7 @@
     <t xml:space="preserve">Uniform scaling</t>
   </si>
   <si>
-    <t xml:space="preserve">YiL1 = rho * YiL0, rho = L1$ / L0$</t>
+    <t xml:space="preserve">y_l1 = rho * y_l, rho = Y1^L$ / Y0^L$</t>
   </si>
   <si>
     <t xml:space="preserve">—</t>
@@ -229,13 +229,13 @@
     <t xml:space="preserve">Expansive</t>
   </si>
   <si>
-    <t xml:space="preserve">Log-affine, sigma_S3 = 1 + k_inequality * gy</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ln(YiL1) = mu1 + sigma_S3 * (ln(YiL0) - mu0); sigma_S3 = 1 + k_inequality * gy; mu1 via uniroot to hit L1$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">k_inequality = 1 by default (config: labor_inequality.k). See labor_inequality sheet for per-variant sigma_S3.</t>
+    <t xml:space="preserve">Log-affine, lambda_S3 = 1 + k_inequality * g_y</t>
+  </si>
+  <si>
+    <t xml:space="preserve">ln(y_l1) = mu1 + lambda_S3 * (ln(y_l) - mu0); lambda_S3 = 1 + k_inequality * g_y; mu1 via uniroot to hit Y1^L$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">k_inequality = 1 by default (config: labor_inequality.k). See labor_inequality sheet for per-variant lambda_S3.</t>
   </si>
   <si>
     <t xml:space="preserve">realization</t>
@@ -349,7 +349,7 @@
     <t xml:space="preserve">Karger 2026 (NBER w35046) Table 39, Total column, 2025.</t>
   </si>
   <si>
-    <t xml:space="preserve">shock.variants.S.s1</t>
+    <t xml:space="preserve">shock.variants.S.theta1_k</t>
   </si>
   <si>
     <t xml:space="preserve">0.45</t>
@@ -367,7 +367,7 @@
     <t xml:space="preserve">Karger 2026 (NBER w35046) Table 19, Slow scenario, median 2030 annualized GDP growth rate.</t>
   </si>
   <si>
-    <t xml:space="preserve">shock.variants.M.s1</t>
+    <t xml:space="preserve">shock.variants.M.theta1_k</t>
   </si>
   <si>
     <t xml:space="preserve">0.462</t>
@@ -385,7 +385,7 @@
     <t xml:space="preserve">Karger 2026 (NBER w35046) Table 19, Moderate scenario, median 2030 annualized GDP growth rate.</t>
   </si>
   <si>
-    <t xml:space="preserve">shock.variants.R.s1</t>
+    <t xml:space="preserve">shock.variants.R.theta1_k</t>
   </si>
   <si>
     <t xml:space="preserve">0.487</t>
@@ -490,31 +490,31 @@
     <t xml:space="preserve">Factor-share mode (R reallocate / F fixed)</t>
   </si>
   <si>
-    <t xml:space="preserve">Post-shock capital share (s1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">AI growth bump over CBO baseline (gy)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Capital growth rate (gk)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor-to-capital growth ratio (alpha)</t>
+    <t xml:space="preserve">Post-shock capital share (theta1_k)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI growth bump over CBO baseline (g_y)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Capital income growth rate (g_k)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor income growth rate (g_l)</t>
   </si>
   <si>
     <t xml:space="preserve">Inequality multiplier (k_inequality)</t>
   </si>
   <si>
-    <t xml:space="preserve">Compressive slope (sigma_S2)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Expansive slope (sigma_S3)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline labor income, $ (L0)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline capital income, $ (K0)</t>
+    <t xml:space="preserve">Compressive slope (lambda_S2)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Expansive slope (lambda_S3)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline labor income, $ (Y0^L)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline capital income, $ (Y0^K)</t>
   </si>
   <si>
     <t xml:space="preserve">Baseline total income, $ (Y0)</t>
@@ -595,31 +595,31 @@
     <t xml:space="preserve">Compressive slope (S2)</t>
   </si>
   <si>
-    <t xml:space="preserve">sigma_S2 = 1 - k_inequality * gy</t>
+    <t xml:space="preserve">lambda_S2 = 1 - k_inequality * g_y</t>
   </si>
   <si>
     <t xml:space="preserve">S: 0.949 | M: 0.933 | R: 0.896  (at k=1)</t>
   </si>
   <si>
-    <t xml:space="preserve">Under the compressive labor scenario (S2), top earners are pulled toward the mean. This is the slope of the log-affine map applied to baseline log labor income; values below 1 compress the distribution. Calculated as 1 - k_inequality * (AI growth bump gy).</t>
+    <t xml:space="preserve">Under the compressive labor scenario (S2), top earners are pulled toward the mean. This is the slope of the log-affine map applied to baseline log labor income; values below 1 compress the distribution. Calculated as 1 - k_inequality * (AI growth bump g_y).</t>
   </si>
   <si>
     <t xml:space="preserve">Expansive slope (S3)</t>
   </si>
   <si>
-    <t xml:space="preserve">sigma_S3 = 1 + k_inequality * gy</t>
+    <t xml:space="preserve">lambda_S3 = 1 + k_inequality * g_y</t>
   </si>
   <si>
     <t xml:space="preserve">S: 1.051 | M: 1.067 | R: 1.104  (at k=1)</t>
   </si>
   <si>
-    <t xml:space="preserve">Under the expansive labor scenario (S3), top earners pull further away from the mean. This is the slope of the log-affine map applied to baseline log labor income; values above 1 stretch the distribution. Calculated as 1 + k_inequality * (AI growth bump gy).</t>
+    <t xml:space="preserve">Under the expansive labor scenario (S3), top earners pull further away from the mean. This is the slope of the log-affine map applied to baseline log labor income; values above 1 stretch the distribution. Calculated as 1 + k_inequality * (AI growth bump g_y).</t>
   </si>
   <si>
     <t xml:space="preserve">Aggregate anchor</t>
   </si>
   <si>
-    <t xml:space="preserve">mu1 via uniroot s.t. sum(weight * exp(mu1 + sigma * (ln(YiL0) - mu0))) = L1$</t>
+    <t xml:space="preserve">mu1 via uniroot s.t. sum(weight * exp(mu1 + lambda * (ln(y_l) - mu0))) = Y1^L$</t>
   </si>
   <si>
     <t xml:space="preserve">varies by cell</t>
@@ -664,19 +664,19 @@
     <t xml:space="preserve">Calibrated corporate-base scale factor</t>
   </si>
   <si>
-    <t xml:space="preserve">eta = tau_stat * (K0$ * kappa_corp) / CBO_CIT$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Calibrated at runtime from K0$</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Single calibrated scale factor that absorbs both the gap between household-realized capital income (K0$) and the pre-realization corporate tax base, and the gap between the statutory rate and the effective rate (avoidance, NOLs, credits, profit shifting). One value per (variant, share_mode) cell.</t>
+    <t xml:space="preserve">eta = tau_stat * (Y0^K$ * kappa_corp) / CBO_CIT$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calibrated at runtime from Y0^K$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Single calibrated scale factor that absorbs both the gap between household-realized capital income (Y0^K$) and the pre-realization corporate tax base, and the gap between the statutory rate and the effective rate (avoidance, NOLs, credits, profit shifting). One value per (variant, share_mode) cell.</t>
   </si>
   <si>
     <t xml:space="preserve">Capital flow (gross)</t>
   </si>
   <si>
-    <t xml:space="preserve">X = K0$ * gk</t>
+    <t xml:space="preserve">X = Y0^K$ * g_k</t>
   </si>
   <si>
     <t xml:space="preserve">varies by variant</t>
@@ -700,7 +700,7 @@
     <t xml:space="preserve">Macro CIT delta</t>
   </si>
   <si>
-    <t xml:space="preserve">delta_R_CIT = tau_stat * kappa_corp * X / eta ≡ X * CBO_CIT$ / K0$</t>
+    <t xml:space="preserve">delta_R_CIT = tau_stat * kappa_corp * X / eta ≡ X * CBO_CIT$ / Y0^K$</t>
   </si>
   <si>
     <t xml:space="preserve">varies by variant only</t>
@@ -916,7 +916,7 @@
     <t xml:space="preserve">Human-readable label for the shock variant, used on plot axes and tables: Slow, Moderate, or Rapid.</t>
   </si>
   <si>
-    <t xml:space="preserve">Factor-share mode. R = reallocate (Karger labor-share decline). F = fixed (labor-capital split preserved; same gy as R, no share reallocation).</t>
+    <t xml:space="preserve">Factor-share mode. R = reallocate (Karger labor-share decline). F = fixed (labor-capital split preserved; same g_y as R, no share reallocation).</t>
   </si>
   <si>
     <t xml:space="preserve">share_mode_label</t>
@@ -1057,19 +1057,19 @@
     <t xml:space="preserve">Karger AI-adoption inputs</t>
   </si>
   <si>
-    <t xml:space="preserve">Karger Table 19 and Table 39 inputs that drive the scenario. r_ai_annual is the AI-conditional annual GDP growth rate from Table 19 (Total / median). 2030 capital share (s_1) and 2030 labor share (1 - s_1) come from Table 39. All three are sourced inputs, not derived. Pulled from config/scenario_params.yaml (shock slice).</t>
+    <t xml:space="preserve">Karger Table 19 and Table 39 inputs that drive the scenario. r_ai_annual is the AI-conditional annual GDP growth rate from Table 19 (Total / median). 2030 capital share (theta1_k) and 2030 labor share (1 - theta1_k) come from Table 39. All three are sourced inputs, not derived. Pulled from config/scenario_params.yaml (shock slice).</t>
   </si>
   <si>
     <t xml:space="preserve">Derived growth bumps</t>
   </si>
   <si>
-    <t xml:space="preserve">Cumulative growth bumps over the Karger 5-year horizon, expressed above the CBO no-AI baseline path (so a value of 0% means the AI shock contributes nothing on top of CBO at the horizon, not that the level is flat). g_y = AI bump on GDP; g_k = implied capital growth bump; labor row = L1_B / L0_B - 1. Negative labor values arise when the labor-share decline outweighs the productivity gain; aggregate labor income levels remain positive (see L0_B / L1_B in cell_params). All three rows are pulled from cell_params (share_mode = R).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Labor-income inequality parameter (sigma)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratio of post- to pre-shock standard deviation of log(YiL) on the positive subset. Compressive = sigma_S2 = 1 - k * g_y; Proportional = sigma_S0 = 1 (no dispersion shift); Expansive = sigma_S3 = 1 + k * g_y. Row labels match the labor_label column elsewhere in the bundle (Compressive = S2, Proportional = S0, Expansive = S3 in cell_params and scenario_id). k is the labor_inequality.k multiplier from config/scenario_params.yaml (default 1.0) and is reported in the sigma section caption.</t>
+    <t xml:space="preserve">Cumulative growth bumps over the Karger 5-year horizon, expressed above the CBO no-AI baseline path (so a value of 0% means the AI shock contributes nothing on top of CBO at the horizon, not that the level is flat). g_y = AI bump on GDP; g_k = implied capital growth bump; labor row = y1_l_B / y0_l_B - 1. Negative labor values arise when the labor-share decline outweighs the productivity gain; aggregate labor income levels remain positive (see y0_l_B / y1_l_B in cell_params). All three rows are pulled from cell_params (share_mode = R).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor-income inequality parameter (lambda)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio of post- to pre-shock standard deviation of log(y_l) on the positive subset. Compressive = lambda_S2 = 1 - k * g_y; Proportional = lambda_S0 = 1 (no dispersion shift); Expansive = lambda_S3 = 1 + k * g_y. Row labels match the labor_label column elsewhere in the bundle (Compressive = S2, Proportional = S0, Expansive = S3 in cell_params and scenario_id). k is the labor_inequality.k multiplier from config/scenario_params.yaml (default 1.0) and is reported in the lambda section caption.</t>
   </si>
   <si>
     <t xml:space="preserve">Notes block</t>
@@ -1084,7 +1084,7 @@
     <t xml:space="preserve">Shock variant code (S = Slow, M = Moderate, R = Rapid).</t>
   </si>
   <si>
-    <t xml:space="preserve">Factor-share mode. R = reallocate (Karger labor-share decline); F = fixed (s1 := 1 - L0, no factor-share shift).</t>
+    <t xml:space="preserve">Factor-share mode. R = reallocate (Karger labor-share decline); F = fixed (theta1_k := theta0_k, no factor-share shift).</t>
   </si>
   <si>
     <t xml:space="preserve">labor_scenario</t>
@@ -1126,49 +1126,49 @@
     <t xml:space="preserve">g_k</t>
   </si>
   <si>
-    <t xml:space="preserve">Implied normalized growth rate of capital (microsim dollars). See §3.2.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">alpha</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Implied normalized growth rate of labor as a multiple of g_k. alpha = 1 under share_mode = F (no reallocation); alpha &lt; 1 under share_mode = R.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">sigma</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Ratio of post- to pre-shock standard deviation of log(YiL) on the positive subset. NA for S0; 1 - k * g_y for S2; 1 + k * g_y for S3. k from labor_inequality.k (default 1).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L0_B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline aggregate labor income in microsim dollars ($ billions). Sum of weight × YiL across tax units.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">L1_B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-shock aggregate labor income in $ billions. L0_B * (1 + alpha * g_k).</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K0_B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Baseline aggregate capital income in microsim dollars ($ billions). Sum of weight × YiK.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">K1_B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Post-shock aggregate capital income in $ billions. K0_B * (1 + g_k).</t>
+    <t xml:space="preserve">Implied cumulative growth rate of capital income over the horizon (microsim dollars). See §3.2.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">g_l</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Implied cumulative growth rate of labor income over the horizon. Equals g_k under share_mode = F (no reallocation); below g_k under share_mode = R.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">lambda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ratio of post- to pre-shock standard deviation of log(y_l) on the positive subset. NA for S0; 1 - k * g_y for S2; 1 + k * g_y for S3. k from labor_inequality.k (default 1).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y0_l_B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline aggregate labor income in microsim dollars ($ billions). Sum of weight × y_l across tax units.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y1_l_B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-shock aggregate labor income in $ billions. y0_l_B * (1 + g_l).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y0_k_B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Baseline aggregate capital income in microsim dollars ($ billions). Sum of weight × y_k.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">y1_k_B</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Post-shock aggregate capital income in $ billions. y0_k_B * (1 + g_k).</t>
   </si>
   <si>
     <t xml:space="preserve">X_B</t>
   </si>
   <si>
-    <t xml:space="preserve">Aggregate AI capital flow in $ billions, before the off-microsim CIT wedge. X = K1_B - K0_B.</t>
+    <t xml:space="preserve">Aggregate AI capital flow in $ billions, before the off-microsim CIT wedge. X = y1_k_B - y0_k_B.</t>
   </si>
   <si>
     <t xml:space="preserve">X_to_units_B</t>
@@ -1189,13 +1189,13 @@
     <t xml:space="preserve">eta_corp</t>
   </si>
   <si>
-    <t xml:space="preserve">Calibrated corporate-base scale factor. eta = cit_statutory * (K0$ * kappa_corp) / CBO_CIT_baseline$ so that the baseline-year CIT level matches CBO. Absorbs both the household-realized-vs-pre-realization wedge and the statutory-vs-effective gap. Constant within a (variant, share_mode) cell.</t>
+    <t xml:space="preserve">Calibrated corporate-base scale factor. eta = cit_statutory * (Y0^K$ * kappa_corp) / CBO_CIT_baseline$ so that the baseline-year CIT level matches CBO. Absorbs both the household-realized-vs-pre-realization wedge and the statutory-vs-effective gap. Constant within a (variant, share_mode) cell.</t>
   </si>
   <si>
     <t xml:space="preserve">delta_R_CIT_B</t>
   </si>
   <si>
-    <t xml:space="preserve">Off-microsim CIT revenue change in $ billions. cit_statutory * kappa_corp * X / eta_corp ≡ X * CBO_CIT_baseline / K0$.</t>
+    <t xml:space="preserve">Off-microsim CIT revenue change in $ billions. cit_statutory * kappa_corp * X / eta_corp ≡ X * CBO_CIT_baseline / Y0^K$.</t>
   </si>
   <si>
     <t xml:space="preserve">revenue_to_gdp</t>
@@ -1456,10 +1456,10 @@
     <t xml:space="preserve">Annual GDP growth under AI (r_ai_annual)</t>
   </si>
   <si>
-    <t xml:space="preserve">2030 capital share (s_1)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2030 labor share (1 - s_1)</t>
+    <t xml:space="preserve">2030 capital share (theta_1_K)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2030 labor share (theta_1_L)</t>
   </si>
   <si>
     <t xml:space="preserve">Cumulative over the Karger 5-year horizon, above the CBO no-AI baseline path.</t>
@@ -1474,7 +1474,7 @@
     <t xml:space="preserve">Labor                (L_1/L_0 - 1)</t>
   </si>
   <si>
-    <t xml:space="preserve">sigma = 1 ± k · g_y on log(YiL);   k = 1.000</t>
+    <t xml:space="preserve">lambda = 1 ± k · g_y on log(y_l);   k = 1.000</t>
   </si>
   <si>
     <t xml:space="preserve">Notes</t>
@@ -1483,46 +1483,70 @@
     <t xml:space="preserve">Baseline labor share (2025): 55.5%. Source: Karger, Buehler, Cox, Saint-Jacques, and Bjorkegren (2026), CBO (2026), and TBL Calculations.</t>
   </si>
   <si>
-    <t xml:space="preserve">Share mode shown: Reallocate (R). The Karger labor-share decline is imposed. Fixed-share (F) twins live in the share_mode_comparison sheet.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Negative labor growth occurs when the labor share falls fast enough to outweigh productivity gains over the horizon. Aggregate labor income levels remain positive - see L0_B / L1_B in cell_params.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">r_ai_annual_target</t>
-  </si>
-  <si>
-    <t xml:space="preserve">delta_rev_to_gdp_cbo_pp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">prod_bump_pp_per_yr</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blsmm_gstar_year_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blsmm_annualized_growth_horizon</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blsmm_year_real_growth</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blsmm_rgfr_year_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blsmm_rgfop_year_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blsmm_debt_year_B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blsmm_gdp_nominal_year_B</t>
-  </si>
-  <si>
-    <t xml:space="preserve">blsmm_debt_to_gdp_year_pct</t>
-  </si>
-  <si>
-    <t xml:space="preserve">delta_debt_to_gdp_vs_baseline_pp</t>
+    <t xml:space="preserve">Share mode shown: Reallocate (R). The Karger labor-share decline is imposed; fixed-share (F) twins are reported separately.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Negative labor growth occurs when the labor share falls fast enough to outweigh productivity gains over the horizon. Aggregate labor income levels remain positive - see y0_l_B / y1_l_B in cell_params.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scenario ID</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Variant</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI Adoption</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share Mode</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Share Mode (label)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Labor Scenario</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Realization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">AI GDP CAGR Target</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Δ Revenue-to-GDP vs CBO (pp)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Productivity Bump (pp/yr)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">GDP Growth g* (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Annualized Growth (2025–Year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Real GDP Growth (Year)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Federal Revenue Path rgfr* (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">rgfop* (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt ($B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Nominal GDP ($B)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Debt-to-GDP (%)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Δ Debt-to-GDP vs Baseline (pp)</t>
   </si>
   <si>
     <t xml:space="preserve">blsmm_baseline</t>
@@ -34890,7 +34914,7 @@
         <v>0.0172117163991912</v>
       </c>
       <c r="J2" t="n">
-        <v>-0.183182342457595</v>
+        <v>-0.00315288252771963</v>
       </c>
       <c r="K2"/>
       <c r="L2" t="n">
@@ -34953,7 +34977,7 @@
         <v>0.0172117163991912</v>
       </c>
       <c r="J3" t="n">
-        <v>-0.183182342457595</v>
+        <v>-0.00315288252771963</v>
       </c>
       <c r="K3" t="n">
         <v>0.994090636005244</v>
@@ -35018,7 +35042,7 @@
         <v>0.0172117163991912</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.183182342457595</v>
+        <v>-0.00315288252771963</v>
       </c>
       <c r="K4" t="n">
         <v>1.00590936399476</v>
@@ -35083,7 +35107,7 @@
         <v>0.0754166612691227</v>
       </c>
       <c r="J5" t="n">
-        <v>0.0545829695654936</v>
+        <v>0.00411646532678367</v>
       </c>
       <c r="K5"/>
       <c r="L5" t="n">
@@ -35146,7 +35170,7 @@
         <v>0.0754166612691227</v>
       </c>
       <c r="J6" t="n">
-        <v>0.0545829695654936</v>
+        <v>0.00411646532678367</v>
       </c>
       <c r="K6" t="n">
         <v>0.964154947478876</v>
@@ -35211,7 +35235,7 @@
         <v>0.0754166612691227</v>
       </c>
       <c r="J7" t="n">
-        <v>0.0545829695654936</v>
+        <v>0.00411646532678367</v>
       </c>
       <c r="K7" t="n">
         <v>1.03584505252112</v>
@@ -35276,7 +35300,7 @@
         <v>0.172812402611785</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.0545835382921483</v>
+        <v>-0.00943271239531852</v>
       </c>
       <c r="K8"/>
       <c r="L8" t="n">
@@ -35339,7 +35363,7 @@
         <v>0.172812402611785</v>
       </c>
       <c r="J9" t="n">
-        <v>-0.0545835382921483</v>
+        <v>-0.00943271239531852</v>
       </c>
       <c r="K9" t="n">
         <v>0.928333636217157</v>
@@ -35404,7 +35428,7 @@
         <v>0.172812402611785</v>
       </c>
       <c r="J10" t="n">
-        <v>-0.0545835382921483</v>
+        <v>-0.00943271239531852</v>
       </c>
       <c r="K10" t="n">
         <v>1.07166636378284</v>
@@ -35469,7 +35493,7 @@
         <v>0.00590936399475563</v>
       </c>
       <c r="J11" t="n">
-        <v>1.00000000000001</v>
+        <v>0.0059093639947557</v>
       </c>
       <c r="K11"/>
       <c r="L11" t="n">
@@ -35532,7 +35556,7 @@
         <v>0.00590936399475563</v>
       </c>
       <c r="J12" t="n">
-        <v>1.00000000000001</v>
+        <v>0.0059093639947557</v>
       </c>
       <c r="K12" t="n">
         <v>0.994090636005244</v>
@@ -35597,7 +35621,7 @@
         <v>0.00590936399475563</v>
       </c>
       <c r="J13" t="n">
-        <v>1.00000000000001</v>
+        <v>0.0059093639947557</v>
       </c>
       <c r="K13" t="n">
         <v>1.00590936399476</v>
@@ -35662,7 +35686,7 @@
         <v>0.0358450525211244</v>
       </c>
       <c r="J14" t="n">
-        <v>1</v>
+        <v>0.0358450525211244</v>
       </c>
       <c r="K14"/>
       <c r="L14" t="n">
@@ -35725,7 +35749,7 @@
         <v>0.0358450525211244</v>
       </c>
       <c r="J15" t="n">
-        <v>1</v>
+        <v>0.0358450525211244</v>
       </c>
       <c r="K15" t="n">
         <v>0.964154947478876</v>
@@ -35790,7 +35814,7 @@
         <v>0.0358450525211244</v>
       </c>
       <c r="J16" t="n">
-        <v>1</v>
+        <v>0.0358450525211244</v>
       </c>
       <c r="K16" t="n">
         <v>1.03584505252112</v>
@@ -35855,7 +35879,7 @@
         <v>0.0716663637828425</v>
       </c>
       <c r="J17" t="n">
-        <v>1</v>
+        <v>0.0716663637828425</v>
       </c>
       <c r="K17"/>
       <c r="L17" t="n">
@@ -35918,7 +35942,7 @@
         <v>0.0716663637828425</v>
       </c>
       <c r="J18" t="n">
-        <v>1</v>
+        <v>0.0716663637828425</v>
       </c>
       <c r="K18" t="n">
         <v>0.928333636217157</v>
@@ -35983,7 +36007,7 @@
         <v>0.0716663637828425</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>0.0716663637828425</v>
       </c>
       <c r="K19" t="n">
         <v>1.07166636378284</v>
@@ -36032,69 +36056,69 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="s">
-        <v>290</v>
+        <v>486</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>30</v>
+        <v>487</v>
       </c>
       <c r="C1" s="1" t="s">
-        <v>293</v>
+        <v>488</v>
       </c>
       <c r="D1" s="1" t="s">
-        <v>43</v>
+        <v>489</v>
       </c>
       <c r="E1" s="1" t="s">
-        <v>296</v>
+        <v>490</v>
       </c>
       <c r="F1" s="1" t="s">
-        <v>53</v>
+        <v>491</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>299</v>
+        <v>492</v>
       </c>
       <c r="H1" s="1" t="s">
-        <v>69</v>
+        <v>493</v>
       </c>
       <c r="I1" s="1" t="s">
-        <v>486</v>
+        <v>494</v>
       </c>
       <c r="J1" s="1" t="s">
-        <v>487</v>
+        <v>495</v>
       </c>
       <c r="K1" s="1" t="s">
-        <v>488</v>
+        <v>496</v>
       </c>
       <c r="L1" s="1" t="s">
-        <v>489</v>
+        <v>497</v>
       </c>
       <c r="M1" s="1" t="s">
-        <v>490</v>
+        <v>498</v>
       </c>
       <c r="N1" s="1" t="s">
-        <v>491</v>
+        <v>499</v>
       </c>
       <c r="O1" s="1" t="s">
-        <v>492</v>
+        <v>500</v>
       </c>
       <c r="P1" s="1" t="s">
-        <v>493</v>
+        <v>501</v>
       </c>
       <c r="Q1" s="1" t="s">
-        <v>494</v>
+        <v>502</v>
       </c>
       <c r="R1" s="1" t="s">
-        <v>495</v>
+        <v>503</v>
       </c>
       <c r="S1" s="1" t="s">
-        <v>496</v>
+        <v>504</v>
       </c>
       <c r="T1" s="1" t="s">
-        <v>497</v>
+        <v>505</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" t="s">
-        <v>498</v>
+        <v>506</v>
       </c>
       <c r="B2"/>
       <c r="C2"/>
@@ -38118,15 +38142,15 @@
   <cols>
     <col min="1" max="1" width="21.71" hidden="0" customWidth="1"/>
     <col min="2" max="2" width="42.71" hidden="0" customWidth="1"/>
-    <col min="3" max="3" width="29.71" hidden="0" customWidth="1"/>
-    <col min="4" max="4" width="37.71" hidden="0" customWidth="1"/>
-    <col min="5" max="5" width="24.71" hidden="0" customWidth="1"/>
-    <col min="6" max="6" width="37.71" hidden="0" customWidth="1"/>
+    <col min="3" max="3" width="35.71" hidden="0" customWidth="1"/>
+    <col min="4" max="4" width="38.71" hidden="0" customWidth="1"/>
+    <col min="5" max="5" width="32.71" hidden="0" customWidth="1"/>
+    <col min="6" max="6" width="30.71" hidden="0" customWidth="1"/>
     <col min="7" max="7" width="36.71" hidden="0" customWidth="1"/>
-    <col min="8" max="8" width="28.71" hidden="0" customWidth="1"/>
-    <col min="9" max="9" width="26.71" hidden="0" customWidth="1"/>
-    <col min="10" max="10" width="29.71" hidden="0" customWidth="1"/>
-    <col min="11" max="11" width="31.71" hidden="0" customWidth="1"/>
+    <col min="8" max="8" width="29.71" hidden="0" customWidth="1"/>
+    <col min="9" max="9" width="27.71" hidden="0" customWidth="1"/>
+    <col min="10" max="10" width="31.71" hidden="0" customWidth="1"/>
+    <col min="11" max="11" width="33.71" hidden="0" customWidth="1"/>
     <col min="12" max="12" width="29.71" hidden="0" customWidth="1"/>
     <col min="13" max="13" width="37.71" hidden="0" customWidth="1"/>
     <col min="14" max="14" width="55.71" hidden="0" customWidth="1"/>
@@ -38249,7 +38273,7 @@
         <v>0.0172117163991912</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.183182342457595</v>
+        <v>-0.00315288252771963</v>
       </c>
       <c r="G2" t="n">
         <v>1</v>
@@ -38335,7 +38359,7 @@
         <v>0.0754166612691227</v>
       </c>
       <c r="F3" t="n">
-        <v>0.0545829695654936</v>
+        <v>0.00411646532678367</v>
       </c>
       <c r="G3" t="n">
         <v>1</v>
@@ -38421,7 +38445,7 @@
         <v>0.172812402611785</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.0545835382921483</v>
+        <v>-0.00943271239531852</v>
       </c>
       <c r="G4" t="n">
         <v>1</v>
@@ -38507,7 +38531,7 @@
         <v>0.00590936399475563</v>
       </c>
       <c r="F5" t="n">
-        <v>1.00000000000001</v>
+        <v>0.0059093639947557</v>
       </c>
       <c r="G5" t="n">
         <v>1</v>
@@ -38593,7 +38617,7 @@
         <v>0.0358450525211244</v>
       </c>
       <c r="F6" t="n">
-        <v>1</v>
+        <v>0.0358450525211244</v>
       </c>
       <c r="G6" t="n">
         <v>1</v>
@@ -38679,7 +38703,7 @@
         <v>0.0716663637828425</v>
       </c>
       <c r="F7" t="n">
-        <v>1</v>
+        <v>0.0716663637828425</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
@@ -38760,7 +38784,7 @@
   <sheetFormatPr defaultRowHeight="15.0" baseColWidth="10"/>
   <cols>
     <col min="1" max="1" width="22.71" hidden="0" customWidth="1"/>
-    <col min="2" max="2" width="76.71" hidden="0" customWidth="1"/>
+    <col min="2" max="2" width="78.71" hidden="0" customWidth="1"/>
     <col min="3" max="3" width="40.71" hidden="0" customWidth="1"/>
     <col min="4" max="4" width="60.71" hidden="0" customWidth="1"/>
   </cols>

--- a/results/aggregates/ai_fiscal_publishable_2030_latest.xlsx
+++ b/results/aggregates/ai_fiscal_publishable_2030_latest.xlsx
@@ -40,7 +40,7 @@
     <t xml:space="preserve">Generated</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-06-30 00:20:46 EDT</t>
+    <t xml:space="preserve">2026-07-09 10:40:56 EDT</t>
   </si>
   <si>
     <t xml:space="preserve">Bundle type</t>
@@ -58,13 +58,13 @@
     <t xml:space="preserve">Tax-Simulator vintage</t>
   </si>
   <si>
-    <t xml:space="preserve">202606300013</t>
+    <t xml:space="preserve">202607091035</t>
   </si>
   <si>
     <t xml:space="preserve">Tax-Simulator output root</t>
   </si>
   <si>
-    <t xml:space="preserve">/nfs/roberts/scratch/pi_nrs36/ji252/model_data/Tax-Simulator/v1/202606300013</t>
+    <t xml:space="preserve">/nfs/roberts/project/pi_nrs36/shared/model_data/Tax-Simulator/v1/202607091035</t>
   </si>
   <si>
     <t xml:space="preserve">Runscript</t>
@@ -94,13 +94,13 @@
     <t xml:space="preserve">AI-Fiscal git rev</t>
   </si>
   <si>
-    <t xml:space="preserve">4a1111ae1e12</t>
+    <t xml:space="preserve">74de5986e5ff</t>
   </si>
   <si>
     <t xml:space="preserve">Orchestrator argv</t>
   </si>
   <si>
-    <t xml:space="preserve">--overwrite --multicore scenario</t>
+    <t xml:space="preserve">--multicore scenario --overwrite</t>
   </si>
   <si>
     <t xml:space="preserve">axis</t>
@@ -298,7 +298,7 @@
     <t xml:space="preserve">sourced</t>
   </si>
   <si>
-    <t xml:space="preserve">CBO 2025 Budget and Economic Outlook (publication 62105), Table 1, real GDP growth for 2026.</t>
+    <t xml:space="preserve">CBO February 2026 Budget and Economic Outlook: 2026 to 2036 (publication 62105), Table 1, real GDP growth for 2026.</t>
   </si>
   <si>
     <t xml:space="preserve">cbo_baseline.g_2027plus</t>
@@ -307,7 +307,7 @@
     <t xml:space="preserve">0.018</t>
   </si>
   <si>
-    <t xml:space="preserve">CBO 2025 Budget and Economic Outlook (publication 62105), Table 1, real GDP growth for 2027 and onward (held flat at 1.8%/yr).</t>
+    <t xml:space="preserve">CBO February 2026 Budget and Economic Outlook: 2026 to 2036 (publication 62105), Table 1, real GDP growth for 2027 and onward (held flat at 1.8%/yr).</t>
   </si>
   <si>
     <t xml:space="preserve">cbo_baseline.gdp_baseline_year_B</t>
@@ -316,7 +316,7 @@
     <t xml:space="preserve">37391</t>
   </si>
   <si>
-    <t xml:space="preserve">CBO 2025 Budget and Economic Outlook (publication 62105), 2030 nominal GDP.</t>
+    <t xml:space="preserve">CBO February 2026 Budget and Economic Outlook: 2026 to 2036 (publication 62105), 2030 nominal GDP.</t>
   </si>
   <si>
     <t xml:space="preserve">cbo_baseline.rev_to_gdp_baseline_year</t>
@@ -325,7 +325,7 @@
     <t xml:space="preserve">0.177</t>
   </si>
   <si>
-    <t xml:space="preserve">CBO 2025 Budget and Economic Outlook (publication 62105), Table 1, 2030 total federal revenue as a share of GDP.</t>
+    <t xml:space="preserve">CBO February 2026 Budget and Economic Outlook: 2026 to 2036 (publication 62105), Table 1, 2030 total federal revenue as a share of GDP.</t>
   </si>
   <si>
     <t xml:space="preserve">cbo_baseline.cit_to_gdp_baseline_year</t>
@@ -334,7 +334,7 @@
     <t xml:space="preserve">0.013</t>
   </si>
   <si>
-    <t xml:space="preserve">CBO 2025 Budget and Economic Outlook (publication 62105), Table 1, 2030 federal corporate-tax revenue as a share of GDP.</t>
+    <t xml:space="preserve">CBO February 2026 Budget and Economic Outlook: 2026 to 2036 (publication 62105), Table 1, 2030 federal corporate-tax revenue as a share of GDP.</t>
   </si>
   <si>
     <t xml:space="preserve">shock</t>
@@ -427,7 +427,7 @@
     <t xml:space="preserve">99.99</t>
   </si>
   <si>
-    <t xml:space="preserve">Smith-Yagan-Zidar 2019 active-profit split, tax-unit-level threshold.</t>
+    <t xml:space="preserve">Saez and Zucman (2020) active-profit split, tax-unit-level threshold.</t>
   </si>
   <si>
     <t xml:space="preserve">passthrough.wage_threshold_conditioning</t>
@@ -436,7 +436,7 @@
     <t xml:space="preserve">positive_wages</t>
   </si>
   <si>
-    <t xml:space="preserve">'positive_wages' matches the W-2 universe per SYZ.</t>
+    <t xml:space="preserve">'positive_wages' matches the W-2 universe per SZ.</t>
   </si>
   <si>
     <t xml:space="preserve">passthrough.active_below_capital_share</t>
@@ -445,7 +445,7 @@
     <t xml:space="preserve">0.25</t>
   </si>
   <si>
-    <t xml:space="preserve">Smith-Yagan-Zidar 2019: 25% of below-W* active profit -&gt; capital.</t>
+    <t xml:space="preserve">Saez and Zucman (2020): 25% of below-W* active profit -&gt; capital.</t>
   </si>
   <si>
     <t xml:space="preserve">passthrough.active_above_capital_share</t>
@@ -454,13 +454,13 @@
     <t xml:space="preserve">0.75</t>
   </si>
   <si>
-    <t xml:space="preserve">Smith-Yagan-Zidar 2019: 75% of above-W* active profit -&gt; capital.</t>
+    <t xml:space="preserve">Saez and Zucman (2020): 75% of above-W* active profit -&gt; capital.</t>
   </si>
   <si>
     <t xml:space="preserve">passthrough.passive_capital_share</t>
   </si>
   <si>
-    <t xml:space="preserve">Smith-Yagan-Zidar 2019: 75% of passive profit -&gt; capital.</t>
+    <t xml:space="preserve">Saez and Zucman (2020): 75% of passive profit -&gt; capital.</t>
   </si>
   <si>
     <t xml:space="preserve">corporate</t>
@@ -793,10 +793,10 @@
     <t xml:space="preserve">proprietors_capital_share</t>
   </si>
   <si>
-    <t xml:space="preserve">Smith-Yagan-Zidar 2019 (passthrough split)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Symmetric SYZ rule averages to ~50% capital across the population</t>
+    <t xml:space="preserve">Saez and Zucman (2020) (passthrough split)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Symmetric SZ rule averages to ~50% capital across the population</t>
   </si>
   <si>
     <t xml:space="preserve">scorp_share_of_BEA_corporate_profits</t>
